--- a/outputs/Approval_Note.xlsx
+++ b/outputs/Approval_Note.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -439,7 +439,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Inspection Approval Note</t>
+          <t>Sample Title</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -511,7 +511,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Inspection Finding</t>
+          <t>Sample</t>
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
@@ -519,7 +519,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Abnormal vibration detected during routine inspection.</t>
+          <t>Test content</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -531,7 +531,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>AI Analysis</t>
+          <t>Source Traceability</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -539,92 +539,29 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>The inspection finding indicates abnormal vibration in the cooling water pump. Based on the available inspection information and referenced maintenance guidance, the pump should be checked for alignment, bearing condition, and coupling issues.</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
+          <t>Source Document</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Sample_Inspection_Report.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Recommended Action</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Inspect pump alignment, bearings, and coupling. Schedule corrective maintenance if abnormal vibration persists.</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>SOP / Knowledge Reference</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>SOP-MECH-014: Centrifugal Pump Inspection and Maintenance</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Source Traceability</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Source Document</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Sample_Inspection_Report.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Source Pages</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>2, 3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A16:B16"/>
+  <mergeCells count="1">
     <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
